--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OREGON_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OREGON_2010.xlsx
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C647">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C990">
